--- a/artfynd/A 52278-2022 artfynd.xlsx
+++ b/artfynd/A 52278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121284505</v>
       </c>
       <c r="B2" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52278-2022 artfynd.xlsx
+++ b/artfynd/A 52278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121284505</v>
       </c>
       <c r="B2" t="n">
-        <v>97035</v>
+        <v>97048</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52278-2022 artfynd.xlsx
+++ b/artfynd/A 52278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121284505</v>
       </c>
       <c r="B2" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52278-2022 artfynd.xlsx
+++ b/artfynd/A 52278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121284505</v>
       </c>
       <c r="B2" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52278-2022 artfynd.xlsx
+++ b/artfynd/A 52278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121284505</v>
       </c>
       <c r="B2" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52278-2022 artfynd.xlsx
+++ b/artfynd/A 52278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121284505</v>
       </c>
       <c r="B2" t="n">
-        <v>97058</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 52278-2022 artfynd.xlsx
+++ b/artfynd/A 52278-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 52278-2022 artfynd.xlsx
+++ b/artfynd/A 52278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121284505</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>97064</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
